--- a/data/trans_orig/P33B_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R2-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32861</t>
+          <t>34654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36645</t>
+          <t>48326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>46842</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60671</t>
+          <t>72273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>385015</t>
+          <t>391575</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>367126</t>
+          <t>373139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394102</t>
+          <t>400859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291483</t>
+          <t>331889</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276555</t>
+          <t>314186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>345377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>676498</t>
+          <t>723463</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>652516</t>
+          <t>698032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690852</t>
+          <t>740846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,67 +1068,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26551</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41743</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>42087</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31430</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>57702</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>6,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>39195</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23394</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>54321</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>65746</t>
+          <t>70616</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48796</t>
+          <t>54259</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87928</t>
+          <t>90223</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -1181,69 +1181,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>396996</t>
+          <t>448360</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>381804</t>
+          <t>434274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407211</t>
+          <t>459099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>94,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>458996</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>443381</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>469653</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>91,6%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>93,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>472309</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>457183</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488110</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>704</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>869305</t>
+          <t>907357</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>847123</t>
+          <t>887750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886255</t>
+          <t>923714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>64131</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45755</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>82866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,67 +1446,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79895</t>
+          <t>94781</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66254</t>
+          <t>79070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94469</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>15,23%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>158911</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>136300</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>183050</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>14,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>17,41%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>139816</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>119584</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>162052</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>476417</t>
+          <t>556706</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>459013</t>
+          <t>537971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>490583</t>
+          <t>572258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,67 +1559,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>462573</t>
+          <t>527358</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447999</t>
+          <t>511160</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>476214</t>
+          <t>543069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,16%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>87,29%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1084065</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1059926</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1106676</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>87,22%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>85,27%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>82,59%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>938990</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>916754</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>959222</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>84,98%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,03%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>103121</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41613</t>
+          <t>85076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137951</t>
+          <t>124001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>151207</t>
+          <t>164381</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124352</t>
+          <t>144846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>171821</t>
+          <t>182089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>244941</t>
+          <t>267502</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149103</t>
+          <t>242418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302415</t>
+          <t>294721</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>794053</t>
+          <t>597496</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>749835</t>
+          <t>576616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>846173</t>
+          <t>615541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>561291</t>
+          <t>572114</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540677</t>
+          <t>554406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>588146</t>
+          <t>591649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1355344</t>
+          <t>1169610</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1297870</t>
+          <t>1142391</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451182</t>
+          <t>1194694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>100735</t>
+          <t>105865</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85689</t>
+          <t>89999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118278</t>
+          <t>124060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>173266</t>
+          <t>196273</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156863</t>
+          <t>177944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189614</t>
+          <t>214211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>274001</t>
+          <t>302138</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250972</t>
+          <t>278893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298200</t>
+          <t>326924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>459469</t>
+          <t>502400</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441926</t>
+          <t>484205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474515</t>
+          <t>518266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>371797</t>
+          <t>411321</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>355449</t>
+          <t>393383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>388200</t>
+          <t>429650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>831266</t>
+          <t>913720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>807067</t>
+          <t>888934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>854295</t>
+          <t>936965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>76105</t>
+          <t>83792</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64285</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88504</t>
+          <t>97309</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>126962</t>
+          <t>140388</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57095</t>
+          <t>126505</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200057</t>
+          <t>154398</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>203066</t>
+          <t>224180</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107656</t>
+          <t>204855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>266112</t>
+          <t>244377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>292060</t>
+          <t>323288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279661</t>
+          <t>309771</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303880</t>
+          <t>336068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>481406</t>
+          <t>298778</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>408311</t>
+          <t>284768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>551273</t>
+          <t>312661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>773467</t>
+          <t>622066</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>710421</t>
+          <t>601869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>868877</t>
+          <t>641391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>81780</t>
+          <t>91064</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>69445</t>
+          <t>78627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>104291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>155682</t>
+          <t>171740</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141442</t>
+          <t>157255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170911</t>
+          <t>189349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>237462</t>
+          <t>262805</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>219709</t>
+          <t>242512</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257281</t>
+          <t>283846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>200979</t>
+          <t>219134</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189682</t>
+          <t>205907</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>213314</t>
+          <t>231571</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>270149</t>
+          <t>292869</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254920</t>
+          <t>275260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284389</t>
+          <t>307354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>471128</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>451309</t>
+          <t>490961</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>488881</t>
+          <t>532295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>354325</t>
+          <t>453359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>534440</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>747925</t>
+          <t>840273</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>596729</t>
+          <t>796552</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>819588</t>
+          <t>882039</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1201720</t>
+          <t>1332994</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1064786</t>
+          <t>1274926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1300366</t>
+          <t>1392435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3004991</t>
+          <t>3038959</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2953708</t>
+          <t>2997240</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3104462</t>
+          <t>3078321</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2911007</t>
+          <t>2893325</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2839344</t>
+          <t>2851559</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3062203</t>
+          <t>2937046</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5915999</t>
+          <t>5932285</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5817353</t>
+          <t>5872844</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6052933</t>
+          <t>5990353</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
